--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.54564549152938</v>
+        <v>5.938667392373524</v>
       </c>
       <c r="D2" t="n">
-        <v>35.11133382373908</v>
+        <v>5.705591746357601</v>
       </c>
       <c r="E2" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F2" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.80881590875511</v>
+        <v>3.868932585172706</v>
       </c>
       <c r="D3" t="n">
-        <v>28.68763712544121</v>
+        <v>4.661741032884197</v>
       </c>
       <c r="E3" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F3" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.81492413612687</v>
+        <v>7.444925172120617</v>
       </c>
       <c r="D4" t="n">
-        <v>45.45313501092078</v>
+        <v>7.386134439274626</v>
       </c>
       <c r="E4" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F4" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.7281554713722</v>
+        <v>6.618325264097982</v>
       </c>
       <c r="D5" t="n">
-        <v>41.60686237555791</v>
+        <v>6.76111513602816</v>
       </c>
       <c r="E5" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F5" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>41.90791341408934</v>
+        <v>6.810035929789518</v>
       </c>
       <c r="D6" t="n">
-        <v>41.77361449989748</v>
+        <v>6.788212356233341</v>
       </c>
       <c r="E6" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F6" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>36.45700746113317</v>
+        <v>5.92426371243414</v>
       </c>
       <c r="D7" t="n">
-        <v>41.67789902489001</v>
+        <v>6.772658591544626</v>
       </c>
       <c r="E7" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F7" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.45259812912826</v>
+        <v>4.623547195983342</v>
       </c>
       <c r="D8" t="n">
-        <v>27.67070824829432</v>
+        <v>4.496490090347828</v>
       </c>
       <c r="E8" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F8" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.08051018834679</v>
+        <v>3.750582905606354</v>
       </c>
       <c r="D9" t="n">
-        <v>22.58635957575446</v>
+        <v>3.6702834310601</v>
       </c>
       <c r="E9" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F9" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.11462522184571</v>
+        <v>4.406126598549928</v>
       </c>
       <c r="D10" t="n">
-        <v>27.50811874913801</v>
+        <v>4.470069296734927</v>
       </c>
       <c r="E10" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F10" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.67369264525415</v>
+        <v>4.496975054853799</v>
       </c>
       <c r="D11" t="n">
-        <v>26.69887195260996</v>
+        <v>4.338566692299118</v>
       </c>
       <c r="E11" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F11" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>41.08328690466767</v>
+        <v>6.676034122008497</v>
       </c>
       <c r="D12" t="n">
-        <v>41.85029439254476</v>
+        <v>6.800672838788524</v>
       </c>
       <c r="E12" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F12" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12.90342644125454</v>
+        <v>2.096806796703863</v>
       </c>
       <c r="D13" t="n">
-        <v>12.68372399703565</v>
+        <v>2.061105149518294</v>
       </c>
       <c r="E13" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F13" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>5.409794015823404</v>
+        <v>0.8790915275713032</v>
       </c>
       <c r="D14" t="n">
-        <v>5.31717641125274</v>
+        <v>0.8640411668285704</v>
       </c>
       <c r="E14" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F14" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.0469698903967</v>
+        <v>6.995132607189463</v>
       </c>
       <c r="D15" t="n">
-        <v>43.98301905968361</v>
+        <v>7.147240597198587</v>
       </c>
       <c r="E15" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F15" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>34.6129964987681</v>
+        <v>5.624611931049816</v>
       </c>
       <c r="D16" t="n">
-        <v>35.59087066244513</v>
+        <v>5.783516482647333</v>
       </c>
       <c r="E16" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F16" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.51434591883445</v>
+        <v>2.683581211810598</v>
       </c>
       <c r="D17" t="n">
-        <v>16.51420117595492</v>
+        <v>2.683557691092675</v>
       </c>
       <c r="E17" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F17" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34.5451175463719</v>
+        <v>5.613581601285434</v>
       </c>
       <c r="D18" t="n">
-        <v>35.56590810941771</v>
+        <v>5.779460067780379</v>
       </c>
       <c r="E18" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F18" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>10.24361771572595</v>
+        <v>1.664587878805467</v>
       </c>
       <c r="D19" t="n">
-        <v>32.31428921954899</v>
+        <v>5.251071998176711</v>
       </c>
       <c r="E19" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F19" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>22.94558781116753</v>
+        <v>3.728658019314724</v>
       </c>
       <c r="D20" t="n">
-        <v>55.29306129833057</v>
+        <v>8.985122460978719</v>
       </c>
       <c r="E20" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F20" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>28.55845318392586</v>
+        <v>4.640748642387953</v>
       </c>
       <c r="D21" t="n">
-        <v>29.1641185167493</v>
+        <v>4.739169258971761</v>
       </c>
       <c r="E21" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F21" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>19.60867155112758</v>
+        <v>3.186409127058232</v>
       </c>
       <c r="D22" t="n">
-        <v>51.80333936368065</v>
+        <v>8.418042646598106</v>
       </c>
       <c r="E22" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F22" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>54.77030157469677</v>
+        <v>8.900174005888227</v>
       </c>
       <c r="D23" t="n">
-        <v>92.49668877143604</v>
+        <v>15.03071192535836</v>
       </c>
       <c r="E23" t="n">
-        <v>12.19282812193943</v>
+        <v>1.981334569815157</v>
       </c>
       <c r="F23" t="n">
-        <v>17.16998887250193</v>
+        <v>2.790123191781563</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
